--- a/R_Codes/DataSummary/All_Prokaryotes/Sample_Type/All_Prokaryotes_Summary_Class_by_Sample_Type.xlsx
+++ b/R_Codes/DataSummary/All_Prokaryotes/Sample_Type/All_Prokaryotes_Summary_Class_by_Sample_Type.xlsx
@@ -900,10 +900,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>16.3403695380059</v>
+        <v>16.3416618666596</v>
       </c>
       <c r="D2" t="n">
-        <v>0.364919314801013</v>
+        <v>0.364966200796807</v>
       </c>
     </row>
     <row r="3">
@@ -914,10 +914,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>6.51788880376076</v>
+        <v>6.51777469517085</v>
       </c>
       <c r="D3" t="n">
-        <v>0.148649506122588</v>
+        <v>0.149483132101543</v>
       </c>
     </row>
     <row r="4">
@@ -928,10 +928,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>6.22723903161778</v>
+        <v>6.22693384084823</v>
       </c>
       <c r="D4" t="n">
-        <v>0.137344309723072</v>
+        <v>0.137333677396879</v>
       </c>
     </row>
     <row r="5">
@@ -942,10 +942,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>5.78196952153187</v>
+        <v>5.78175384328398</v>
       </c>
       <c r="D5" t="n">
-        <v>0.173895046899155</v>
+        <v>0.173891851031029</v>
       </c>
     </row>
     <row r="6">
@@ -956,10 +956,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>4.75112364897646</v>
+        <v>4.75077424714615</v>
       </c>
       <c r="D6" t="n">
-        <v>0.129801582746227</v>
+        <v>0.129793138447533</v>
       </c>
     </row>
     <row r="7">
@@ -970,10 +970,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>4.29688870687125</v>
+        <v>4.29551016526434</v>
       </c>
       <c r="D7" t="n">
-        <v>0.760395363004059</v>
+        <v>0.760088335441991</v>
       </c>
     </row>
     <row r="8">
@@ -984,10 +984,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>3.56531569965563</v>
+        <v>3.56579486530789</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0709566502638378</v>
+        <v>0.0709657729581015</v>
       </c>
     </row>
     <row r="9">
@@ -998,10 +998,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>3.40976468453934</v>
+        <v>3.40983508152703</v>
       </c>
       <c r="D9" t="n">
-        <v>0.197089448395916</v>
+        <v>0.197090472795478</v>
       </c>
     </row>
     <row r="10">
@@ -1012,10 +1012,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>3.25289332287214</v>
+        <v>3.2527788563025</v>
       </c>
       <c r="D10" t="n">
-        <v>0.108663499471417</v>
+        <v>0.108659565304884</v>
       </c>
     </row>
     <row r="11">
@@ -1026,10 +1026,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>3.15596309415241</v>
+        <v>3.15587678225824</v>
       </c>
       <c r="D11" t="n">
-        <v>0.174451677946733</v>
+        <v>0.174437328289574</v>
       </c>
     </row>
     <row r="12">
@@ -1040,10 +1040,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>2.94775463378045</v>
+        <v>2.94806372159539</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0717211799235303</v>
+        <v>0.07173198581819</v>
       </c>
     </row>
     <row r="13">
@@ -1054,10 +1054,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>2.72620662807857</v>
+        <v>2.72609495261659</v>
       </c>
       <c r="D13" t="n">
-        <v>0.104650557514979</v>
+        <v>0.104642971896762</v>
       </c>
     </row>
     <row r="14">
@@ -1068,10 +1068,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>2.65454340488704</v>
+        <v>2.65450884006315</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0501338485760552</v>
+        <v>0.0501332455260786</v>
       </c>
     </row>
     <row r="15">
@@ -1082,10 +1082,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>2.38729825062195</v>
+        <v>2.38739613161961</v>
       </c>
       <c r="D15" t="n">
-        <v>0.319167766070598</v>
+        <v>0.319182762232658</v>
       </c>
     </row>
     <row r="16">
@@ -1096,10 +1096,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>2.36803476006497</v>
+        <v>2.36796288589534</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0847669645851135</v>
+        <v>0.0847630239866693</v>
       </c>
     </row>
     <row r="17">
@@ -1110,10 +1110,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>2.26675503353507</v>
+        <v>2.26695125312262</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0418533205527473</v>
+        <v>0.0418574721223817</v>
       </c>
     </row>
     <row r="18">
@@ -1124,10 +1124,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>2.16120215614226</v>
+        <v>2.16190915247882</v>
       </c>
       <c r="D18" t="n">
-        <v>0.630839632185262</v>
+        <v>0.631046876611651</v>
       </c>
     </row>
     <row r="19">
@@ -1138,10 +1138,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>1.78431039450407</v>
+        <v>1.78449052469228</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0132479013162543</v>
+        <v>0.0132512817326122</v>
       </c>
     </row>
     <row r="20">
@@ -1152,10 +1152,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>1.60443809805352</v>
+        <v>1.6045568246363</v>
       </c>
       <c r="D20" t="n">
-        <v>1.02470187994274</v>
+        <v>1.02480571441199</v>
       </c>
     </row>
     <row r="21">
@@ -1166,10 +1166,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>1.56894865858386</v>
+        <v>1.568986544644</v>
       </c>
       <c r="D21" t="n">
-        <v>0.158045752393243</v>
+        <v>0.158054034060133</v>
       </c>
     </row>
     <row r="22">
@@ -1180,10 +1180,10 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>1.3671290596746</v>
+        <v>1.36706008764098</v>
       </c>
       <c r="D22" t="n">
-        <v>0.024602274813773</v>
+        <v>0.0246008624733284</v>
       </c>
     </row>
     <row r="23">
@@ -1194,10 +1194,10 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>1.30185458681485</v>
+        <v>1.30212288353511</v>
       </c>
       <c r="D23" t="n">
-        <v>0.12398872214353</v>
+        <v>0.124013734188933</v>
       </c>
     </row>
     <row r="24">
@@ -1208,10 +1208,10 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>1.15782568183839</v>
+        <v>1.15781211665459</v>
       </c>
       <c r="D24" t="n">
-        <v>0.388147454124298</v>
+        <v>0.388147147303828</v>
       </c>
     </row>
     <row r="25">
@@ -1222,10 +1222,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>1.10313487400028</v>
+        <v>1.1032148757848</v>
       </c>
       <c r="D25" t="n">
-        <v>0.091316681498599</v>
+        <v>0.091329827462734</v>
       </c>
     </row>
     <row r="26">
@@ -1236,10 +1236,10 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.914810625981458</v>
+        <v>0.914748471908951</v>
       </c>
       <c r="D26" t="n">
-        <v>0.112719322261636</v>
+        <v>0.112713526040406</v>
       </c>
     </row>
     <row r="27">
@@ -1250,10 +1250,10 @@
         <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>0.86366333890105</v>
+        <v>0.86376269509832</v>
       </c>
       <c r="D27" t="n">
-        <v>0.131172557706573</v>
+        <v>0.131190806078947</v>
       </c>
     </row>
     <row r="28">
@@ -1264,10 +1264,10 @@
         <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>0.815602824465873</v>
+        <v>0.814399947104209</v>
       </c>
       <c r="D28" t="n">
-        <v>0.094353123616174</v>
+        <v>0.100056472702307</v>
       </c>
     </row>
     <row r="29">
@@ -1278,10 +1278,10 @@
         <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>0.719770124787197</v>
+        <v>0.719736577546547</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0138090172437913</v>
+        <v>0.0138080383445599</v>
       </c>
     </row>
     <row r="30">
@@ -1292,10 +1292,10 @@
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.637769836102387</v>
+        <v>0.637767957096375</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0637842852856246</v>
+        <v>0.0637833909765124</v>
       </c>
     </row>
     <row r="31">
@@ -1306,10 +1306,10 @@
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>0.630804205125401</v>
+        <v>0.630698100890269</v>
       </c>
       <c r="D31" t="n">
-        <v>0.21514285032078</v>
+        <v>0.215099761008479</v>
       </c>
     </row>
     <row r="32">
@@ -1320,10 +1320,10 @@
         <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>0.608494449146302</v>
+        <v>0.608625642131184</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0501820178937106</v>
+        <v>0.0501922784259376</v>
       </c>
     </row>
     <row r="33">
@@ -1334,10 +1334,10 @@
         <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>0.601069402914586</v>
+        <v>0.601109066988274</v>
       </c>
       <c r="D33" t="n">
-        <v>0.114916725818998</v>
+        <v>0.114931127079321</v>
       </c>
     </row>
     <row r="34">
@@ -1348,10 +1348,10 @@
         <v>37</v>
       </c>
       <c r="C34" t="n">
-        <v>0.564366858239162</v>
+        <v>0.564317099847651</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0274906116577773</v>
+        <v>0.0274888222439849</v>
       </c>
     </row>
     <row r="35">
@@ -1362,10 +1362,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.55395138987645</v>
+        <v>0.553986634179406</v>
       </c>
       <c r="D35" t="n">
-        <v>0.017223332453407</v>
+        <v>0.0172252220198623</v>
       </c>
     </row>
     <row r="36">
@@ -1376,10 +1376,10 @@
         <v>39</v>
       </c>
       <c r="C36" t="n">
-        <v>0.53364988089015</v>
+        <v>0.533610796502323</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0672478275891398</v>
+        <v>0.0672437902588174</v>
       </c>
     </row>
     <row r="37">
@@ -1390,10 +1390,10 @@
         <v>40</v>
       </c>
       <c r="C37" t="n">
-        <v>0.406629786645901</v>
+        <v>0.406617206121492</v>
       </c>
       <c r="D37" t="n">
-        <v>0.17598432539977</v>
+        <v>0.175977369525517</v>
       </c>
     </row>
     <row r="38">
@@ -1404,10 +1404,10 @@
         <v>41</v>
       </c>
       <c r="C38" t="n">
-        <v>0.393257124299549</v>
+        <v>0.393317167573086</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0144218386698097</v>
+        <v>0.0144237310221212</v>
       </c>
     </row>
     <row r="39">
@@ -1418,10 +1418,10 @@
         <v>42</v>
       </c>
       <c r="C39" t="n">
-        <v>0.376478799111195</v>
+        <v>0.376460428719311</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0569277071811371</v>
+        <v>0.0569255066041069</v>
       </c>
     </row>
     <row r="40">
@@ -1432,10 +1432,10 @@
         <v>43</v>
       </c>
       <c r="C40" t="n">
-        <v>0.375992656868376</v>
+        <v>0.376090634527935</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0119771154406029</v>
+        <v>0.0119805882665518</v>
       </c>
     </row>
     <row r="41">
@@ -1446,10 +1446,10 @@
         <v>44</v>
       </c>
       <c r="C41" t="n">
-        <v>0.319907100323329</v>
+        <v>0.319966284722752</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0792373807900135</v>
+        <v>0.0792516795713162</v>
       </c>
     </row>
     <row r="42">
@@ -1460,10 +1460,10 @@
         <v>45</v>
       </c>
       <c r="C42" t="n">
-        <v>0.311547220728577</v>
+        <v>0.311533277594606</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0172972008546067</v>
+        <v>0.017295263988654</v>
       </c>
     </row>
     <row r="43">
@@ -1474,10 +1474,10 @@
         <v>46</v>
       </c>
       <c r="C43" t="n">
-        <v>0.286951946092299</v>
+        <v>0.287017555621548</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0167429224293851</v>
+        <v>0.0167476611580681</v>
       </c>
     </row>
     <row r="44">
@@ -1488,10 +1488,10 @@
         <v>47</v>
       </c>
       <c r="C44" t="n">
-        <v>0.257536867560212</v>
+        <v>0.257546713674983</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00630636905983868</v>
+        <v>0.00630700331476103</v>
       </c>
     </row>
     <row r="45">
@@ -1502,10 +1502,10 @@
         <v>48</v>
       </c>
       <c r="C45" t="n">
-        <v>0.250044031462655</v>
+        <v>0.250047245262464</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0225874571938306</v>
+        <v>0.022589536277193</v>
       </c>
     </row>
     <row r="46">
@@ -1516,10 +1516,10 @@
         <v>49</v>
       </c>
       <c r="C46" t="n">
-        <v>0.240955188548261</v>
+        <v>0.240932634902632</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0196478778738606</v>
+        <v>0.019645659674528</v>
       </c>
     </row>
     <row r="47">
@@ -1530,10 +1530,10 @@
         <v>50</v>
       </c>
       <c r="C47" t="n">
-        <v>0.236651365549334</v>
+        <v>0.236621238972088</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0245403392704892</v>
+        <v>0.0245344346007489</v>
       </c>
     </row>
     <row r="48">
@@ -1544,10 +1544,10 @@
         <v>51</v>
       </c>
       <c r="C48" t="n">
-        <v>0.234992180800151</v>
+        <v>0.235017760704586</v>
       </c>
       <c r="D48" t="n">
-        <v>0.00760673412748419</v>
+        <v>0.00760762449770051</v>
       </c>
     </row>
     <row r="49">
@@ -1558,10 +1558,10 @@
         <v>52</v>
       </c>
       <c r="C49" t="n">
-        <v>0.230585283865868</v>
+        <v>0.230564123421666</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0509844526870072</v>
+        <v>0.0509783767753283</v>
       </c>
     </row>
     <row r="50">
@@ -1572,10 +1572,10 @@
         <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>0.219742906044752</v>
+        <v>0.21975122573986</v>
       </c>
       <c r="D50" t="n">
-        <v>0.00600844586702114</v>
+        <v>0.0060086872243454</v>
       </c>
     </row>
     <row r="51">
@@ -1586,10 +1586,10 @@
         <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>0.180419394007164</v>
+        <v>0.18040569029904</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0166865917056073</v>
+        <v>0.0166850776816214</v>
       </c>
     </row>
     <row r="52">
@@ -1600,10 +1600,10 @@
         <v>55</v>
       </c>
       <c r="C52" t="n">
-        <v>0.180274979366738</v>
+        <v>0.180255950866786</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0482170531919115</v>
+        <v>0.048211338126906</v>
       </c>
     </row>
     <row r="53">
@@ -1614,10 +1614,10 @@
         <v>56</v>
       </c>
       <c r="C53" t="n">
-        <v>0.175302426010932</v>
+        <v>0.175282668877571</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0704758478739547</v>
+        <v>0.0704671562035202</v>
       </c>
     </row>
     <row r="54">
@@ -1628,10 +1628,10 @@
         <v>57</v>
       </c>
       <c r="C54" t="n">
-        <v>0.168522161421196</v>
+        <v>0.168502071930805</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0229008601942342</v>
+        <v>0.0228979232440653</v>
       </c>
     </row>
     <row r="55">
@@ -1642,10 +1642,10 @@
         <v>58</v>
       </c>
       <c r="C55" t="n">
-        <v>0.161638211676001</v>
+        <v>0.161676597587428</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0265707855618042</v>
+        <v>0.0265770666322205</v>
       </c>
     </row>
     <row r="56">
@@ -1656,10 +1656,10 @@
         <v>59</v>
       </c>
       <c r="C56" t="n">
-        <v>0.159943909553694</v>
+        <v>0.15995203921521</v>
       </c>
       <c r="D56" t="n">
-        <v>0.00568762009029767</v>
+        <v>0.00568780060194871</v>
       </c>
     </row>
     <row r="57">
@@ -1670,10 +1670,10 @@
         <v>60</v>
       </c>
       <c r="C57" t="n">
-        <v>0.159462823768081</v>
+        <v>0.15945461104189</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0288106145615336</v>
+        <v>0.0288087319627314</v>
       </c>
     </row>
     <row r="58">
@@ -1684,10 +1684,10 @@
         <v>61</v>
       </c>
       <c r="C58" t="n">
-        <v>0.158651012341907</v>
+        <v>0.158673366659809</v>
       </c>
       <c r="D58" t="n">
-        <v>0.045737570407468</v>
+        <v>0.0457539772131932</v>
       </c>
     </row>
     <row r="59">
@@ -1698,10 +1698,10 @@
         <v>62</v>
       </c>
       <c r="C59" t="n">
-        <v>0.140466714222925</v>
+        <v>0.14047524908631</v>
       </c>
       <c r="D59" t="n">
-        <v>0.00788768201295411</v>
+        <v>0.00788783623797873</v>
       </c>
     </row>
     <row r="60">
@@ -1712,10 +1712,10 @@
         <v>63</v>
       </c>
       <c r="C60" t="n">
-        <v>0.137410891541032</v>
+        <v>0.137395260037261</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0449355261351212</v>
+        <v>0.0449289816918205</v>
       </c>
     </row>
     <row r="61">
@@ -1726,10 +1726,10 @@
         <v>64</v>
       </c>
       <c r="C61" t="n">
-        <v>0.135808327999466</v>
+        <v>0.135806111433529</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0204445409249088</v>
+        <v>0.0204457783616086</v>
       </c>
     </row>
     <row r="62">
@@ -1740,10 +1740,10 @@
         <v>65</v>
       </c>
       <c r="C62" t="n">
-        <v>0.110803758156809</v>
+        <v>0.110803736305645</v>
       </c>
       <c r="D62" t="n">
-        <v>0.00364327926675692</v>
+        <v>0.00364336006938954</v>
       </c>
     </row>
     <row r="63">
@@ -1754,10 +1754,10 @@
         <v>66</v>
       </c>
       <c r="C63" t="n">
-        <v>0.096861716502859</v>
+        <v>0.0968590850529563</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0098797210525114</v>
+        <v>0.00987867127821817</v>
       </c>
     </row>
     <row r="64">
@@ -1768,10 +1768,10 @@
         <v>67</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0957017874459538</v>
+        <v>0.0957086574341561</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0295079921162402</v>
+        <v>0.0295107728838257</v>
       </c>
     </row>
     <row r="65">
@@ -1782,10 +1782,10 @@
         <v>68</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0882387344369958</v>
+        <v>0.0882681183753547</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0214519495552798</v>
+        <v>0.0214593103647159</v>
       </c>
     </row>
     <row r="66">
@@ -1796,10 +1796,10 @@
         <v>69</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0854309559855238</v>
+        <v>0.0854199033065721</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0133012523857728</v>
+        <v>0.0132973407545517</v>
       </c>
     </row>
     <row r="67">
@@ -1810,10 +1810,10 @@
         <v>70</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0812239280245435</v>
+        <v>0.0812389184245935</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0116606661657457</v>
+        <v>0.0116625794027242</v>
       </c>
     </row>
     <row r="68">
@@ -1824,7 +1824,7 @@
         <v>71</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0735733971407114</v>
+        <v>0.0735541085857273</v>
       </c>
       <c r="D68"/>
     </row>
@@ -1836,10 +1836,10 @@
         <v>72</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0692411801897809</v>
+        <v>0.0692410464152097</v>
       </c>
       <c r="D69" t="n">
-        <v>0.0243421446622777</v>
+        <v>0.0243414152156006</v>
       </c>
     </row>
     <row r="70">
@@ -1850,10 +1850,10 @@
         <v>73</v>
       </c>
       <c r="C70" t="n">
-        <v>0.067218041652683</v>
+        <v>0.0672108440905825</v>
       </c>
       <c r="D70" t="n">
-        <v>0.00668684478327204</v>
+        <v>0.00668616124790953</v>
       </c>
     </row>
     <row r="71">
@@ -1864,7 +1864,7 @@
         <v>74</v>
       </c>
       <c r="C71" t="n">
-        <v>0.06156481136528</v>
+        <v>0.0615545147950379</v>
       </c>
       <c r="D71"/>
     </row>
@@ -1876,10 +1876,10 @@
         <v>75</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0575685432085077</v>
+        <v>0.0575790883844144</v>
       </c>
       <c r="D72" t="n">
-        <v>0.00404441216473035</v>
+        <v>0.00404498640104643</v>
       </c>
     </row>
     <row r="73">
@@ -1890,10 +1890,10 @@
         <v>76</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0558564601377837</v>
+        <v>0.0558554742148481</v>
       </c>
       <c r="D73" t="n">
-        <v>0.0072784081124607</v>
+        <v>0.00727819198305638</v>
       </c>
     </row>
     <row r="74">
@@ -1904,10 +1904,10 @@
         <v>77</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0444333676544535</v>
+        <v>0.044441119444064</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0027361000168165</v>
+        <v>0.00273663123169244</v>
       </c>
     </row>
     <row r="75">
@@ -1918,10 +1918,10 @@
         <v>78</v>
       </c>
       <c r="C75" t="n">
-        <v>0.041275304519162</v>
+        <v>0.0412794290949981</v>
       </c>
       <c r="D75" t="n">
-        <v>0.0080909810456354</v>
+        <v>0.00809159300126105</v>
       </c>
     </row>
     <row r="76">
@@ -1932,10 +1932,10 @@
         <v>79</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0412210726264895</v>
+        <v>0.0412218327332593</v>
       </c>
       <c r="D76" t="n">
-        <v>0.00275171881252815</v>
+        <v>0.0027513876411545</v>
       </c>
     </row>
     <row r="77">
@@ -1946,10 +1946,10 @@
         <v>80</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0394546465321653</v>
+        <v>0.0394545630763963</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0048306054789954</v>
+        <v>0.00483024384608776</v>
       </c>
     </row>
     <row r="78">
@@ -1960,10 +1960,10 @@
         <v>81</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0379787166826076</v>
+        <v>0.0379799407001521</v>
       </c>
       <c r="D78" t="n">
-        <v>0.00304539560801592</v>
+        <v>0.00304531061956671</v>
       </c>
     </row>
     <row r="79">
@@ -1974,10 +1974,10 @@
         <v>82</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0360922136210034</v>
+        <v>0.0360885361652888</v>
       </c>
       <c r="D79" t="n">
-        <v>0.00329405287532919</v>
+        <v>0.00329315460379549</v>
       </c>
     </row>
     <row r="80">
@@ -1988,10 +1988,10 @@
         <v>83</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0357424290263582</v>
+        <v>0.0357480677974404</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00168638120545988</v>
+        <v>0.00168680940639728</v>
       </c>
     </row>
     <row r="81">
@@ -2002,10 +2002,10 @@
         <v>84</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0351413218389282</v>
+        <v>0.035147110580455</v>
       </c>
       <c r="D81" t="n">
-        <v>0.00223147331606697</v>
+        <v>0.00223192621137626</v>
       </c>
     </row>
     <row r="82">
@@ -2016,10 +2016,10 @@
         <v>85</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0326582679579259</v>
+        <v>0.0326619136604909</v>
       </c>
       <c r="D82" t="n">
-        <v>0.00209412826448036</v>
+        <v>0.00209457650402667</v>
       </c>
     </row>
     <row r="83">
@@ -2030,7 +2030,7 @@
         <v>86</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0316309736631204</v>
+        <v>0.0316297890797849</v>
       </c>
       <c r="D83"/>
     </row>
@@ -2042,10 +2042,10 @@
         <v>87</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0313758170533332</v>
+        <v>0.0313841297664091</v>
       </c>
       <c r="D84" t="n">
-        <v>0.00523947935992204</v>
+        <v>0.00524152469478577</v>
       </c>
     </row>
     <row r="85">
@@ -2056,10 +2056,10 @@
         <v>88</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0298202618941446</v>
+        <v>0.0298250290235258</v>
       </c>
       <c r="D85" t="n">
-        <v>0.00668946759658577</v>
+        <v>0.00669114910307872</v>
       </c>
     </row>
     <row r="86">
@@ -2070,10 +2070,10 @@
         <v>89</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0297184103989921</v>
+        <v>0.0297134464866567</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0166486551989316</v>
+        <v>0.0166461770143964</v>
       </c>
     </row>
     <row r="87">
@@ -2084,10 +2084,10 @@
         <v>90</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0295457685029536</v>
+        <v>0.0295461004520193</v>
       </c>
       <c r="D87" t="n">
-        <v>0.00598291523636964</v>
+        <v>0.00598137732196592</v>
       </c>
     </row>
     <row r="88">
@@ -2098,10 +2098,10 @@
         <v>91</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0294915921757449</v>
+        <v>0.0294900037062563</v>
       </c>
       <c r="D88" t="n">
-        <v>0.00836889204896852</v>
+        <v>0.00836874621831844</v>
       </c>
     </row>
     <row r="89">
@@ -2112,7 +2112,7 @@
         <v>92</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0289973929406735</v>
+        <v>0.028990242796974</v>
       </c>
       <c r="D89"/>
     </row>
@@ -2124,10 +2124,10 @@
         <v>93</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0256712998428392</v>
+        <v>0.0256698708611311</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0038681151108631</v>
+        <v>0.00386771393409036</v>
       </c>
     </row>
     <row r="91">
@@ -2138,10 +2138,10 @@
         <v>94</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0256615203212098</v>
+        <v>0.0256641501038899</v>
       </c>
       <c r="D91" t="n">
-        <v>0.00664478539283624</v>
+        <v>0.00664577834495545</v>
       </c>
     </row>
     <row r="92">
@@ -2152,10 +2152,10 @@
         <v>95</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0216161878598986</v>
+        <v>0.0216140206011366</v>
       </c>
       <c r="D92" t="n">
-        <v>0.00500467422972252</v>
+        <v>0.00500333103498446</v>
       </c>
     </row>
     <row r="93">
@@ -2166,10 +2166,10 @@
         <v>96</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0206172319516331</v>
+        <v>0.0206166093532046</v>
       </c>
       <c r="D93" t="n">
-        <v>0.00906946714473541</v>
+        <v>0.0090693907818614</v>
       </c>
     </row>
     <row r="94">
@@ -2180,10 +2180,10 @@
         <v>97</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0197244616446968</v>
+        <v>0.0197225605249409</v>
       </c>
       <c r="D94" t="n">
-        <v>0.00670892909133827</v>
+        <v>0.0067068795102041</v>
       </c>
     </row>
     <row r="95">
@@ -2194,10 +2194,10 @@
         <v>98</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0194367992385843</v>
+        <v>0.0194313573189654</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0134471690570031</v>
+        <v>0.0134430571653996</v>
       </c>
     </row>
     <row r="96">
@@ -2208,10 +2208,10 @@
         <v>99</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0191004059207158</v>
+        <v>0.0190963875430284</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0127808770907428</v>
+        <v>0.0127783505917011</v>
       </c>
     </row>
     <row r="97">
@@ -2222,10 +2222,10 @@
         <v>100</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0186067067748186</v>
+        <v>0.0186067906975823</v>
       </c>
       <c r="D97" t="n">
-        <v>0.00246551259817442</v>
+        <v>0.00246572573655409</v>
       </c>
     </row>
     <row r="98">
@@ -2236,10 +2236,10 @@
         <v>101</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0183543284382216</v>
+        <v>0.0183576322802629</v>
       </c>
       <c r="D98" t="n">
-        <v>0.00293734422480663</v>
+        <v>0.00293824038624759</v>
       </c>
     </row>
     <row r="99">
@@ -2250,10 +2250,10 @@
         <v>102</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0178994139860595</v>
+        <v>0.0179009714449529</v>
       </c>
       <c r="D99" t="n">
-        <v>0.00235547475936501</v>
+        <v>0.00235512932184248</v>
       </c>
     </row>
     <row r="100">
@@ -2264,10 +2264,10 @@
         <v>103</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0176228646727078</v>
+        <v>0.0176228204521005</v>
       </c>
       <c r="D100" t="n">
-        <v>0.00507237707616203</v>
+        <v>0.00507194153967515</v>
       </c>
     </row>
     <row r="101">
@@ -2278,10 +2278,10 @@
         <v>104</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0165665652057967</v>
+        <v>0.016564924693143</v>
       </c>
       <c r="D101" t="n">
-        <v>0.00185358351927208</v>
+        <v>0.00185341504255475</v>
       </c>
     </row>
     <row r="102">
@@ -2292,10 +2292,10 @@
         <v>105</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0163720305170195</v>
+        <v>0.0163773060721655</v>
       </c>
       <c r="D102" t="n">
-        <v>0.0106598070644074</v>
+        <v>0.0106630716517072</v>
       </c>
     </row>
     <row r="103">
@@ -2306,10 +2306,10 @@
         <v>106</v>
       </c>
       <c r="C103" t="n">
-        <v>0.016284070387818</v>
+        <v>0.0162848852949877</v>
       </c>
       <c r="D103" t="n">
-        <v>0.00229361056036175</v>
+        <v>0.00229383266052794</v>
       </c>
     </row>
     <row r="104">
@@ -2320,10 +2320,10 @@
         <v>107</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0149113256045441</v>
+        <v>0.0149099596104707</v>
       </c>
       <c r="D104" t="n">
-        <v>0.00273498055236116</v>
+        <v>0.00273402095514348</v>
       </c>
     </row>
     <row r="105">
@@ -2334,10 +2334,10 @@
         <v>108</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0140552285037183</v>
+        <v>0.0140572890748737</v>
       </c>
       <c r="D105" t="n">
-        <v>0.00201327935472589</v>
+        <v>0.0020135781075336</v>
       </c>
     </row>
     <row r="106">
@@ -2348,10 +2348,10 @@
         <v>109</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0114864371120666</v>
+        <v>0.0114842257669918</v>
       </c>
       <c r="D106" t="n">
-        <v>0.00438291868901427</v>
+        <v>0.00438250764268453</v>
       </c>
     </row>
     <row r="107">
@@ -2362,10 +2362,10 @@
         <v>110</v>
       </c>
       <c r="C107" t="n">
-        <v>0.00994805168119341</v>
+        <v>0.00995011862370593</v>
       </c>
       <c r="D107" t="n">
-        <v>0.000865244098210358</v>
+        <v>0.000865407396954317</v>
       </c>
     </row>
     <row r="108">
@@ -2376,10 +2376,10 @@
         <v>111</v>
       </c>
       <c r="C108" t="n">
-        <v>0.00946857729403005</v>
+        <v>0.00946940839145006</v>
       </c>
       <c r="D108" t="n">
-        <v>0.000598209856622833</v>
+        <v>0.000598048541075432</v>
       </c>
     </row>
     <row r="109">
@@ -2390,7 +2390,7 @@
         <v>112</v>
       </c>
       <c r="C109" t="n">
-        <v>0.00861631421020671</v>
+        <v>0.00861351645857161</v>
       </c>
       <c r="D109"/>
     </row>
@@ -2402,10 +2402,10 @@
         <v>113</v>
       </c>
       <c r="C110" t="n">
-        <v>0.00781217081803749</v>
+        <v>0.00781499872210221</v>
       </c>
       <c r="D110" t="n">
-        <v>0.000517222988787047</v>
+        <v>0.000518019480477547</v>
       </c>
     </row>
     <row r="111">
@@ -2416,7 +2416,7 @@
         <v>114</v>
       </c>
       <c r="C111" t="n">
-        <v>0.00779227838199572</v>
+        <v>0.00779161582114557</v>
       </c>
       <c r="D111"/>
     </row>
@@ -2428,7 +2428,7 @@
         <v>115</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0077399357150925</v>
+        <v>0.00773785181134503</v>
       </c>
       <c r="D112"/>
     </row>
@@ -2440,10 +2440,10 @@
         <v>116</v>
       </c>
       <c r="C113" t="n">
-        <v>0.00773643509087286</v>
+        <v>0.00773685206736114</v>
       </c>
       <c r="D113" t="n">
-        <v>0.00132693872080473</v>
+        <v>0.00132690765332156</v>
       </c>
     </row>
     <row r="114">
@@ -2454,10 +2454,10 @@
         <v>117</v>
       </c>
       <c r="C114" t="n">
-        <v>0.00764347406992903</v>
+        <v>0.00764209855422093</v>
       </c>
       <c r="D114" t="n">
-        <v>0.00492737014416636</v>
+        <v>0.00492660482862357</v>
       </c>
     </row>
     <row r="115">
@@ -2468,7 +2468,7 @@
         <v>118</v>
       </c>
       <c r="C115" t="n">
-        <v>0.00654644511804976</v>
+        <v>0.00654815647051074</v>
       </c>
       <c r="D115"/>
     </row>
@@ -2480,10 +2480,10 @@
         <v>119</v>
       </c>
       <c r="C116" t="n">
-        <v>0.00617037805902535</v>
+        <v>0.00616903133528503</v>
       </c>
       <c r="D116" t="n">
-        <v>0.00362955849553183</v>
+        <v>0.00362821786694141</v>
       </c>
     </row>
     <row r="117">
@@ -2494,7 +2494,7 @@
         <v>120</v>
       </c>
       <c r="C117" t="n">
-        <v>0.00591344335439638</v>
+        <v>0.00591442986738659</v>
       </c>
       <c r="D117"/>
     </row>
@@ -2506,10 +2506,10 @@
         <v>121</v>
       </c>
       <c r="C118" t="n">
-        <v>0.00558355119579296</v>
+        <v>0.00558395893937707</v>
       </c>
       <c r="D118" t="n">
-        <v>0.00115410349329897</v>
+        <v>0.00115438021349579</v>
       </c>
     </row>
     <row r="119">
@@ -2520,7 +2520,7 @@
         <v>122</v>
       </c>
       <c r="C119" t="n">
-        <v>0.00543441349094345</v>
+        <v>0.00543327530447121</v>
       </c>
       <c r="D119"/>
     </row>
@@ -2532,10 +2532,10 @@
         <v>123</v>
       </c>
       <c r="C120" t="n">
-        <v>0.00539629558277401</v>
+        <v>0.00539634031839956</v>
       </c>
       <c r="D120" t="n">
-        <v>0.00123235214220535</v>
+        <v>0.00123234364749038</v>
       </c>
     </row>
     <row r="121">
@@ -2546,7 +2546,7 @@
         <v>124</v>
       </c>
       <c r="C121" t="n">
-        <v>0.00483597344577606</v>
+        <v>0.00483387324479411</v>
       </c>
       <c r="D121"/>
     </row>
@@ -2558,10 +2558,10 @@
         <v>125</v>
       </c>
       <c r="C122" t="n">
-        <v>0.0034267777182468</v>
+        <v>0.00342706683545743</v>
       </c>
       <c r="D122" t="n">
-        <v>0.000356041595137824</v>
+        <v>0.000356207481303227</v>
       </c>
     </row>
     <row r="123">
@@ -2572,7 +2572,7 @@
         <v>126</v>
       </c>
       <c r="C123" t="n">
-        <v>0.00311466650806061</v>
+        <v>0.00311398034450118</v>
       </c>
       <c r="D123"/>
     </row>
@@ -2584,7 +2584,7 @@
         <v>127</v>
       </c>
       <c r="C124" t="n">
-        <v>0.00275271307684238</v>
+        <v>0.00275229518766117</v>
       </c>
       <c r="D124"/>
     </row>
@@ -2596,10 +2596,10 @@
         <v>128</v>
       </c>
       <c r="C125" t="n">
-        <v>0.00266553086413415</v>
+        <v>0.00266576179172187</v>
       </c>
       <c r="D125" t="n">
-        <v>0.000251896828010007</v>
+        <v>0.000251605887793505</v>
       </c>
     </row>
     <row r="126">
@@ -2610,10 +2610,10 @@
         <v>129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.0025260615499865</v>
+        <v>0.00252568655131178</v>
       </c>
       <c r="D126" t="n">
-        <v>0.000212051995630788</v>
+        <v>0.000211449346693792</v>
       </c>
     </row>
     <row r="127">
@@ -2624,7 +2624,7 @@
         <v>130</v>
       </c>
       <c r="C127" t="n">
-        <v>0.00231958028649142</v>
+        <v>0.00231857292264834</v>
       </c>
       <c r="D127"/>
     </row>
@@ -2636,7 +2636,7 @@
         <v>131</v>
       </c>
       <c r="C128" t="n">
-        <v>0.00227296086236</v>
+        <v>0.00227236253405944</v>
       </c>
       <c r="D128"/>
     </row>
@@ -2648,7 +2648,7 @@
         <v>132</v>
       </c>
       <c r="C129" t="n">
-        <v>0.00188394705026929</v>
+        <v>0.0018831288763299</v>
       </c>
       <c r="D129"/>
     </row>
@@ -2660,7 +2660,7 @@
         <v>133</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0014965446366289</v>
+        <v>0.00149683890921961</v>
       </c>
       <c r="D130"/>
     </row>
@@ -2672,10 +2672,10 @@
         <v>134</v>
       </c>
       <c r="C131" t="n">
-        <v>0.00148515371654911</v>
+        <v>0.0014857306427319</v>
       </c>
       <c r="D131" t="n">
-        <v>0.000138327611613312</v>
+        <v>0.00013819619213571</v>
       </c>
     </row>
     <row r="132">
@@ -2686,7 +2686,7 @@
         <v>135</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0014532035748619</v>
+        <v>0.00145329450458777</v>
       </c>
       <c r="D132"/>
     </row>
@@ -2698,10 +2698,10 @@
         <v>136</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0013258475318235</v>
+        <v>0.00132621593596831</v>
       </c>
       <c r="D133" t="n">
-        <v>0.000595529386284204</v>
+        <v>0.000595938407639598</v>
       </c>
     </row>
     <row r="134">
@@ -2712,7 +2712,7 @@
         <v>137</v>
       </c>
       <c r="C134" t="n">
-        <v>0.00131995759266029</v>
+        <v>0.00131999530673519</v>
       </c>
       <c r="D134"/>
     </row>
@@ -2724,10 +2724,10 @@
         <v>138</v>
       </c>
       <c r="C135" t="n">
-        <v>0.00128045054789576</v>
+        <v>0.00128144962202281</v>
       </c>
       <c r="D135" t="n">
-        <v>0.000133274109538564</v>
+        <v>0.00013329477761492</v>
       </c>
     </row>
     <row r="136">
@@ -2738,7 +2738,7 @@
         <v>139</v>
       </c>
       <c r="C136" t="n">
-        <v>0.00123255311809684</v>
+        <v>0.00123373961745808</v>
       </c>
       <c r="D136"/>
     </row>
@@ -2750,10 +2750,10 @@
         <v>140</v>
       </c>
       <c r="C137" t="n">
-        <v>0.00112481168378119</v>
+        <v>0.00112432319255408</v>
       </c>
       <c r="D137" t="n">
-        <v>0.000128351294167125</v>
+        <v>0.000128295552853185</v>
       </c>
     </row>
     <row r="138">
@@ -2764,7 +2764,7 @@
         <v>141</v>
       </c>
       <c r="C138" t="n">
-        <v>0.00103740720921775</v>
+        <v>0.00103790087927966</v>
       </c>
       <c r="D138"/>
     </row>
@@ -2776,7 +2776,7 @@
         <v>142</v>
       </c>
       <c r="C139" t="n">
-        <v>0.000922997919245635</v>
+        <v>0.000922597073137179</v>
       </c>
       <c r="D139"/>
     </row>
@@ -2788,10 +2788,10 @@
         <v>143</v>
       </c>
       <c r="C140" t="n">
-        <v>0.000919275033170778</v>
+        <v>0.000919209051858425</v>
       </c>
       <c r="D140" t="n">
-        <v>0.000204861794556036</v>
+        <v>0.000204537183800384</v>
       </c>
     </row>
     <row r="141">
@@ -2802,10 +2802,10 @@
         <v>144</v>
       </c>
       <c r="C141" t="n">
-        <v>0.000907717416699578</v>
+        <v>0.000908211868035587</v>
       </c>
       <c r="D141" t="n">
-        <v>0.0000917045317402739</v>
+        <v>0.0000917432529488665</v>
       </c>
     </row>
     <row r="142">
@@ -2816,7 +2816,7 @@
         <v>145</v>
       </c>
       <c r="C142" t="n">
-        <v>0.000839983116322694</v>
+        <v>0.000839618322473947</v>
       </c>
       <c r="D142"/>
     </row>
@@ -2828,7 +2828,7 @@
         <v>146</v>
       </c>
       <c r="C143" t="n">
-        <v>0.000820479638527545</v>
+        <v>0.000820123314788007</v>
       </c>
       <c r="D143"/>
     </row>
@@ -2840,10 +2840,10 @@
         <v>147</v>
       </c>
       <c r="C144" t="n">
-        <v>0.00065094940846202</v>
+        <v>0.000651444288172053</v>
       </c>
       <c r="D144" t="n">
-        <v>0.0000151269257583571</v>
+        <v>0.0000151989036349364</v>
       </c>
     </row>
     <row r="145">
@@ -2854,7 +2854,7 @@
         <v>148</v>
       </c>
       <c r="C145" t="n">
-        <v>0.000560266571534148</v>
+        <v>0.000560800833632297</v>
       </c>
       <c r="D145"/>
     </row>
@@ -2866,7 +2866,7 @@
         <v>149</v>
       </c>
       <c r="C146" t="n">
-        <v>0.000470972871201373</v>
+        <v>0.000470768333749366</v>
       </c>
       <c r="D146"/>
     </row>
@@ -2878,7 +2878,7 @@
         <v>150</v>
       </c>
       <c r="C147" t="n">
-        <v>0.000389013812090704</v>
+        <v>0.000389233657729537</v>
       </c>
       <c r="D147"/>
     </row>
@@ -2890,7 +2890,7 @@
         <v>151</v>
       </c>
       <c r="C148" t="n">
-        <v>0.00033617105601325</v>
+        <v>0.000336469391912891</v>
       </c>
       <c r="D148"/>
     </row>
@@ -2927,10 +2927,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>12.3777284875815</v>
+        <v>12.4894590005171</v>
       </c>
       <c r="D2" t="n">
-        <v>0.233262486217937</v>
+        <v>0.23636106801239</v>
       </c>
     </row>
     <row r="3">
@@ -2941,10 +2941,10 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>12.0996076308437</v>
+        <v>12.2938896280527</v>
       </c>
       <c r="D3" t="n">
-        <v>2.29176087600768</v>
+        <v>2.33014365957232</v>
       </c>
     </row>
     <row r="4">
@@ -2955,10 +2955,10 @@
         <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>8.67920809365492</v>
+        <v>8.8112952152606</v>
       </c>
       <c r="D4" t="n">
-        <v>2.28619312956589</v>
+        <v>2.321077297726</v>
       </c>
     </row>
     <row r="5">
@@ -2969,10 +2969,10 @@
         <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>7.29857903009211</v>
+        <v>7.02613892299157</v>
       </c>
       <c r="D5" t="n">
-        <v>0.48956399296486</v>
+        <v>0.465930570105285</v>
       </c>
     </row>
     <row r="6">
@@ -2983,10 +2983,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="n">
-        <v>6.43457936383208</v>
+        <v>6.4990922487162</v>
       </c>
       <c r="D6" t="n">
-        <v>0.518854068435167</v>
+        <v>0.523843098151598</v>
       </c>
     </row>
     <row r="7">
@@ -2997,10 +2997,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>6.00059437757851</v>
+        <v>6.04000279408516</v>
       </c>
       <c r="D7" t="n">
-        <v>0.126756726742976</v>
+        <v>0.127291476514302</v>
       </c>
     </row>
     <row r="8">
@@ -3011,10 +3011,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.91568048612496</v>
+        <v>5.96085242465855</v>
       </c>
       <c r="D8" t="n">
-        <v>0.173828352321236</v>
+        <v>0.175282910053269</v>
       </c>
     </row>
     <row r="9">
@@ -3025,10 +3025,10 @@
         <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>5.36838357745397</v>
+        <v>5.42361890298193</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05326214873936</v>
+        <v>0.0537982409071878</v>
       </c>
     </row>
     <row r="10">
@@ -3039,10 +3039,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>4.51132800477803</v>
+        <v>4.55770284259195</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0774952974275796</v>
+        <v>0.0782957107496393</v>
       </c>
     </row>
     <row r="11">
@@ -3053,10 +3053,10 @@
         <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>3.56762833346748</v>
+        <v>3.60183314118872</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0779809671398668</v>
+        <v>0.0787157120239988</v>
       </c>
     </row>
     <row r="12">
@@ -3064,13 +3064,13 @@
         <v>152</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>2.88889806711582</v>
+        <v>2.47014871151312</v>
       </c>
       <c r="D12" t="n">
-        <v>0.265536307089052</v>
+        <v>0.0506833935769615</v>
       </c>
     </row>
     <row r="13">
@@ -3078,13 +3078,13 @@
         <v>152</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>2.44593337876785</v>
+        <v>2.27684735802708</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0501965925298373</v>
+        <v>0.261012795580897</v>
       </c>
     </row>
     <row r="14">
@@ -3095,10 +3095,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>1.96056103238851</v>
+        <v>1.98238244503224</v>
       </c>
       <c r="D14" t="n">
-        <v>0.276209985670932</v>
+        <v>0.279390314080453</v>
       </c>
     </row>
     <row r="15">
@@ -3109,10 +3109,10 @@
         <v>100</v>
       </c>
       <c r="C15" t="n">
-        <v>1.29544938331861</v>
+        <v>1.29557691708346</v>
       </c>
       <c r="D15" t="n">
-        <v>0.155325666761689</v>
+        <v>0.155894122034182</v>
       </c>
     </row>
     <row r="16">
@@ -3123,10 +3123,10 @@
         <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>1.28514251661013</v>
+        <v>1.28677439767439</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0280538192757856</v>
+        <v>0.0281743852971031</v>
       </c>
     </row>
     <row r="17">
@@ -3137,10 +3137,10 @@
         <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>1.25345259694664</v>
+        <v>1.26113808801741</v>
       </c>
       <c r="D17" t="n">
-        <v>0.12983801045033</v>
+        <v>0.131020992824456</v>
       </c>
     </row>
     <row r="18">
@@ -3151,10 +3151,10 @@
         <v>32</v>
       </c>
       <c r="C18" t="n">
-        <v>0.913580062960667</v>
+        <v>0.923176232746477</v>
       </c>
       <c r="D18" t="n">
-        <v>0.093826376811375</v>
+        <v>0.0948126436621205</v>
       </c>
     </row>
     <row r="19">
@@ -3165,10 +3165,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>0.835467851231246</v>
+        <v>0.843785264834105</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0135068681137793</v>
+        <v>0.0136366010387442</v>
       </c>
     </row>
     <row r="20">
@@ -3179,10 +3179,10 @@
         <v>41</v>
       </c>
       <c r="C20" t="n">
-        <v>0.788271969213215</v>
+        <v>0.772484808234929</v>
       </c>
       <c r="D20" t="n">
-        <v>0.031042212941511</v>
+        <v>0.0297954421072885</v>
       </c>
     </row>
     <row r="21">
@@ -3193,10 +3193,10 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>0.762039082652275</v>
+        <v>0.768228944722999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0202773380830396</v>
+        <v>0.0204534592447282</v>
       </c>
     </row>
     <row r="22">
@@ -3207,10 +3207,10 @@
         <v>24</v>
       </c>
       <c r="C22" t="n">
-        <v>0.728093027628316</v>
+        <v>0.726377064849629</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0886693576228797</v>
+        <v>0.0877294763493455</v>
       </c>
     </row>
     <row r="23">
@@ -3221,10 +3221,10 @@
         <v>17</v>
       </c>
       <c r="C23" t="n">
-        <v>0.611937454293534</v>
+        <v>0.617899697480469</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0229257232687582</v>
+        <v>0.0231710099600266</v>
       </c>
     </row>
     <row r="24">
@@ -3235,10 +3235,10 @@
         <v>58</v>
       </c>
       <c r="C24" t="n">
-        <v>0.558052680413921</v>
+        <v>0.563390110406617</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0678834815202903</v>
+        <v>0.0685115467636428</v>
       </c>
     </row>
     <row r="25">
@@ -3249,10 +3249,10 @@
         <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>0.539940742373557</v>
+        <v>0.54571878241808</v>
       </c>
       <c r="D25" t="n">
-        <v>0.024583978825797</v>
+        <v>0.0248336220151589</v>
       </c>
     </row>
     <row r="26">
@@ -3263,10 +3263,10 @@
         <v>9</v>
       </c>
       <c r="C26" t="n">
-        <v>0.53231820900024</v>
+        <v>0.537452727145315</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0128969765074405</v>
+        <v>0.0130265086890308</v>
       </c>
     </row>
     <row r="27">
@@ -3277,10 +3277,10 @@
         <v>23</v>
       </c>
       <c r="C27" t="n">
-        <v>0.530249905132421</v>
+        <v>0.535897075431976</v>
       </c>
       <c r="D27" t="n">
-        <v>0.138525410573065</v>
+        <v>0.139977746502613</v>
       </c>
     </row>
     <row r="28">
@@ -3291,10 +3291,10 @@
         <v>36</v>
       </c>
       <c r="C28" t="n">
-        <v>0.508663718367773</v>
+        <v>0.513947278718301</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0785202334983789</v>
+        <v>0.0793479837468379</v>
       </c>
     </row>
     <row r="29">
@@ -3305,10 +3305,10 @@
         <v>30</v>
       </c>
       <c r="C29" t="n">
-        <v>0.502394483652806</v>
+        <v>0.507431702016306</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0613094177263046</v>
+        <v>0.0619300384488777</v>
       </c>
     </row>
     <row r="30">
@@ -3319,10 +3319,10 @@
         <v>116</v>
       </c>
       <c r="C30" t="n">
-        <v>0.499642068352108</v>
+        <v>0.504622302772785</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0431474871161018</v>
+        <v>0.0435913093659496</v>
       </c>
     </row>
     <row r="31">
@@ -3333,10 +3333,10 @@
         <v>70</v>
       </c>
       <c r="C31" t="n">
-        <v>0.480397425228766</v>
+        <v>0.483510492761259</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0559039825327892</v>
+        <v>0.0563888807995842</v>
       </c>
     </row>
     <row r="32">
@@ -3347,10 +3347,10 @@
         <v>68</v>
       </c>
       <c r="C32" t="n">
-        <v>0.445538702653705</v>
+        <v>0.449720615143711</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0439004825324316</v>
+        <v>0.0443152857058187</v>
       </c>
     </row>
     <row r="33">
@@ -3361,10 +3361,10 @@
         <v>44</v>
       </c>
       <c r="C33" t="n">
-        <v>0.433138109768814</v>
+        <v>0.437249810629596</v>
       </c>
       <c r="D33" t="n">
-        <v>0.170918567060812</v>
+        <v>0.172544225154919</v>
       </c>
     </row>
     <row r="34">
@@ -3375,10 +3375,10 @@
         <v>35</v>
       </c>
       <c r="C34" t="n">
-        <v>0.403673298238749</v>
+        <v>0.407542227995152</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0328982787996362</v>
+        <v>0.033211432227416</v>
       </c>
     </row>
     <row r="35">
@@ -3389,10 +3389,10 @@
         <v>29</v>
       </c>
       <c r="C35" t="n">
-        <v>0.37088930739431</v>
+        <v>0.374891186203305</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0596733269801258</v>
+        <v>0.0603501710173934</v>
       </c>
     </row>
     <row r="36">
@@ -3403,10 +3403,10 @@
         <v>25</v>
       </c>
       <c r="C36" t="n">
-        <v>0.347650292461376</v>
+        <v>0.351507383903775</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0071911833103883</v>
+        <v>0.00728115924108556</v>
       </c>
     </row>
     <row r="37">
@@ -3417,10 +3417,10 @@
         <v>83</v>
       </c>
       <c r="C37" t="n">
-        <v>0.322559052162815</v>
+        <v>0.325872129306395</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0110423899584782</v>
+        <v>0.0111491770541813</v>
       </c>
     </row>
     <row r="38">
@@ -3431,10 +3431,10 @@
         <v>63</v>
       </c>
       <c r="C38" t="n">
-        <v>0.311623189052691</v>
+        <v>0.314669483987686</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0220995333354377</v>
+        <v>0.0223099636957097</v>
       </c>
     </row>
     <row r="39">
@@ -3445,10 +3445,10 @@
         <v>144</v>
       </c>
       <c r="C39" t="n">
-        <v>0.299751638190769</v>
+        <v>0.302745918686671</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0420631559551596</v>
+        <v>0.0424844998248838</v>
       </c>
     </row>
     <row r="40">
@@ -3459,10 +3459,10 @@
         <v>13</v>
       </c>
       <c r="C40" t="n">
-        <v>0.299189189074616</v>
+        <v>0.302291075757152</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0124053908964905</v>
+        <v>0.0125311384130672</v>
       </c>
     </row>
     <row r="41">
@@ -3473,10 +3473,10 @@
         <v>62</v>
       </c>
       <c r="C41" t="n">
-        <v>0.23405589994846</v>
+        <v>0.23645064239872</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0144627977790964</v>
+        <v>0.0146088301600629</v>
       </c>
     </row>
     <row r="42">
@@ -3487,10 +3487,10 @@
         <v>53</v>
       </c>
       <c r="C42" t="n">
-        <v>0.213153446507115</v>
+        <v>0.215393044492356</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0123975404435767</v>
+        <v>0.0125185883348391</v>
       </c>
     </row>
     <row r="43">
@@ -3501,10 +3501,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>0.194899228057228</v>
+        <v>0.196711440813216</v>
       </c>
       <c r="D43" t="n">
-        <v>0.091666968535913</v>
+        <v>0.0925166929574372</v>
       </c>
     </row>
     <row r="44">
@@ -3515,10 +3515,10 @@
         <v>74</v>
       </c>
       <c r="C44" t="n">
-        <v>0.193949528009353</v>
+        <v>0.195970272665752</v>
       </c>
       <c r="D44" t="n">
-        <v>0.106489376473915</v>
+        <v>0.107557432972455</v>
       </c>
     </row>
     <row r="45">
@@ -3529,10 +3529,10 @@
         <v>110</v>
       </c>
       <c r="C45" t="n">
-        <v>0.192073904333453</v>
+        <v>0.185606422179952</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0385324957204959</v>
+        <v>0.0363825452082465</v>
       </c>
     </row>
     <row r="46">
@@ -3543,10 +3543,10 @@
         <v>46</v>
       </c>
       <c r="C46" t="n">
-        <v>0.183752846879863</v>
+        <v>0.182984374584332</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0106122976844663</v>
+        <v>0.0104886642945894</v>
       </c>
     </row>
     <row r="47">
@@ -3557,10 +3557,10 @@
         <v>130</v>
       </c>
       <c r="C47" t="n">
-        <v>0.173458613479594</v>
+        <v>0.175951998261204</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0684884422434154</v>
+        <v>0.06952476620221</v>
       </c>
     </row>
     <row r="48">
@@ -3571,10 +3571,10 @@
         <v>45</v>
       </c>
       <c r="C48" t="n">
-        <v>0.156631291605068</v>
+        <v>0.155081482625821</v>
       </c>
       <c r="D48" t="n">
-        <v>0.00988841897842502</v>
+        <v>0.00957300588467285</v>
       </c>
     </row>
     <row r="49">
@@ -3585,10 +3585,10 @@
         <v>80</v>
       </c>
       <c r="C49" t="n">
-        <v>0.121468435479933</v>
+        <v>0.11818721558921</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0370623980907105</v>
+        <v>0.0359403375213512</v>
       </c>
     </row>
     <row r="50">
@@ -3599,10 +3599,10 @@
         <v>140</v>
       </c>
       <c r="C50" t="n">
-        <v>0.110420006924664</v>
+        <v>0.11155802917118</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0313909523245771</v>
+        <v>0.0317103665692805</v>
       </c>
     </row>
     <row r="51">
@@ -3613,10 +3613,10 @@
         <v>56</v>
       </c>
       <c r="C51" t="n">
-        <v>0.107639211163976</v>
+        <v>0.108794356659839</v>
       </c>
       <c r="D51" t="n">
-        <v>0.028744368517691</v>
+        <v>0.0290445478347597</v>
       </c>
     </row>
     <row r="52">
@@ -3627,10 +3627,10 @@
         <v>21</v>
       </c>
       <c r="C52" t="n">
-        <v>0.101126518365119</v>
+        <v>0.102106311384776</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0157067411332251</v>
+        <v>0.0158547105903662</v>
       </c>
     </row>
     <row r="53">
@@ -3641,10 +3641,10 @@
         <v>64</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0990262976006827</v>
+        <v>0.100003263321802</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0121570348357733</v>
+        <v>0.0122719910044211</v>
       </c>
     </row>
     <row r="54">
@@ -3655,10 +3655,10 @@
         <v>54</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0987132006294671</v>
+        <v>0.099773327672455</v>
       </c>
       <c r="D54" t="n">
-        <v>0.00622806908915873</v>
+        <v>0.00629639076465932</v>
       </c>
     </row>
     <row r="55">
@@ -3669,10 +3669,10 @@
         <v>67</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0935175524530813</v>
+        <v>0.0944420890475745</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0368839010250521</v>
+        <v>0.0372485283916166</v>
       </c>
     </row>
     <row r="56">
@@ -3683,10 +3683,10 @@
         <v>27</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0890420250863173</v>
+        <v>0.09001137746645</v>
       </c>
       <c r="D56" t="n">
-        <v>0.019072714477922</v>
+        <v>0.019300954403762</v>
       </c>
     </row>
     <row r="57">
@@ -3697,10 +3697,10 @@
         <v>71</v>
       </c>
       <c r="C57" t="n">
-        <v>0.088546212222615</v>
+        <v>0.0886310901280696</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0182082430319726</v>
+        <v>0.0183931047776126</v>
       </c>
     </row>
     <row r="58">
@@ -3711,10 +3711,10 @@
         <v>128</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0810488108774321</v>
+        <v>0.0818029015103466</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0394587927912284</v>
+        <v>0.039824487345065</v>
       </c>
     </row>
     <row r="59">
@@ -3725,10 +3725,10 @@
         <v>117</v>
       </c>
       <c r="C59" t="n">
-        <v>0.079910122766446</v>
+        <v>0.0808196308559792</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0447853982793154</v>
+        <v>0.0452965340806616</v>
       </c>
     </row>
     <row r="60">
@@ -3739,10 +3739,10 @@
         <v>120</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0786202353082748</v>
+        <v>0.0795922373678087</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0348025089453629</v>
+        <v>0.0352438227503994</v>
       </c>
     </row>
     <row r="61">
@@ -3753,10 +3753,10 @@
         <v>47</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0758282964359459</v>
+        <v>0.0762795297972343</v>
       </c>
       <c r="D61" t="n">
-        <v>0.00179354153556445</v>
+        <v>0.00179389654034583</v>
       </c>
     </row>
     <row r="62">
@@ -3767,10 +3767,10 @@
         <v>69</v>
       </c>
       <c r="C62" t="n">
-        <v>0.074039126402663</v>
+        <v>0.0747947017657944</v>
       </c>
       <c r="D62" t="n">
-        <v>0.00606339646283336</v>
+        <v>0.00612372977989521</v>
       </c>
     </row>
     <row r="63">
@@ -3781,10 +3781,10 @@
         <v>28</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0730662949453925</v>
+        <v>0.0738608168801044</v>
       </c>
       <c r="D63" t="n">
-        <v>0.00790033664291753</v>
+        <v>0.00799110880951997</v>
       </c>
     </row>
     <row r="64">
@@ -3795,10 +3795,10 @@
         <v>33</v>
       </c>
       <c r="C64" t="n">
-        <v>0.071126792992777</v>
+        <v>0.0718269762375084</v>
       </c>
       <c r="D64" t="n">
-        <v>0.00786309949772369</v>
+        <v>0.00793661066492192</v>
       </c>
     </row>
     <row r="65">
@@ -3806,13 +3806,13 @@
         <v>152</v>
       </c>
       <c r="B65" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0711195866690807</v>
+        <v>0.06993559108947</v>
       </c>
       <c r="D65" t="n">
-        <v>0.00656720286960041</v>
+        <v>0.00334388252238749</v>
       </c>
     </row>
     <row r="66">
@@ -3820,13 +3820,13 @@
         <v>152</v>
       </c>
       <c r="B66" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0704629215431186</v>
+        <v>0.0696937804075641</v>
       </c>
       <c r="D66" t="n">
-        <v>0.00347427723818621</v>
+        <v>0.00619216063132812</v>
       </c>
     </row>
     <row r="67">
@@ -3837,10 +3837,10 @@
         <v>77</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0687520201922047</v>
+        <v>0.0694585919082762</v>
       </c>
       <c r="D67" t="n">
-        <v>0.00495698776500924</v>
+        <v>0.00500934688503574</v>
       </c>
     </row>
     <row r="68">
@@ -3851,10 +3851,10 @@
         <v>84</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0672231007563641</v>
+        <v>0.0680899551216883</v>
       </c>
       <c r="D68" t="n">
-        <v>0.00654081050116582</v>
+        <v>0.00663812124548857</v>
       </c>
     </row>
     <row r="69">
@@ -3865,7 +3865,7 @@
         <v>153</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0616720518196562</v>
+        <v>0.0622869477174784</v>
       </c>
       <c r="D69"/>
     </row>
@@ -3877,10 +3877,10 @@
         <v>65</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0613624690433296</v>
+        <v>0.0618795824701197</v>
       </c>
       <c r="D70" t="n">
-        <v>0.00527434026977243</v>
+        <v>0.00533405300317862</v>
       </c>
     </row>
     <row r="71">
@@ -3891,10 +3891,10 @@
         <v>154</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0533832448887809</v>
+        <v>0.0542827492590861</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0276755548138828</v>
+        <v>0.0281609770856999</v>
       </c>
     </row>
     <row r="72">
@@ -3905,10 +3905,10 @@
         <v>105</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0527591416698914</v>
+        <v>0.0533696063962407</v>
       </c>
       <c r="D72" t="n">
-        <v>0.00534601674185898</v>
+        <v>0.00540637165680088</v>
       </c>
     </row>
     <row r="73">
@@ -3919,10 +3919,10 @@
         <v>101</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0482915546042372</v>
+        <v>0.0488006595589728</v>
       </c>
       <c r="D73" t="n">
-        <v>0.00706137599549996</v>
+        <v>0.00713049837984519</v>
       </c>
     </row>
     <row r="74">
@@ -3933,10 +3933,10 @@
         <v>34</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0469127446703312</v>
+        <v>0.0473806391248837</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0151960570885899</v>
+        <v>0.0153517835288353</v>
       </c>
     </row>
     <row r="75">
@@ -3944,13 +3944,13 @@
         <v>152</v>
       </c>
       <c r="B75" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C75" t="n">
-        <v>0.045370413465389</v>
+        <v>0.0453527023264522</v>
       </c>
       <c r="D75" t="n">
-        <v>0.00247003681816374</v>
+        <v>0.00623168390849019</v>
       </c>
     </row>
     <row r="76">
@@ -3958,13 +3958,13 @@
         <v>152</v>
       </c>
       <c r="B76" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0449692614462909</v>
+        <v>0.0453505024149384</v>
       </c>
       <c r="D76" t="n">
-        <v>0.00616517559552406</v>
+        <v>0.00244234498401862</v>
       </c>
     </row>
     <row r="77">
@@ -3972,13 +3972,13 @@
         <v>152</v>
       </c>
       <c r="B77" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0437813523651193</v>
+        <v>0.0437035992699299</v>
       </c>
       <c r="D77" t="n">
-        <v>0.00795095344513261</v>
+        <v>0.0222554464346034</v>
       </c>
     </row>
     <row r="78">
@@ -3986,13 +3986,13 @@
         <v>152</v>
       </c>
       <c r="B78" t="s">
-        <v>155</v>
+        <v>52</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0432833375691765</v>
+        <v>0.0432826304881083</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0220403411555036</v>
+        <v>0.0140210130386968</v>
       </c>
     </row>
     <row r="79">
@@ -4000,13 +4000,13 @@
         <v>152</v>
       </c>
       <c r="B79" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0428041170433677</v>
+        <v>0.0432651434363811</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0138642850309527</v>
+        <v>0.00638709212430936</v>
       </c>
     </row>
     <row r="80">
@@ -4014,13 +4014,13 @@
         <v>152</v>
       </c>
       <c r="B80" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0428040503181483</v>
+        <v>0.0423879399442869</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00632149963574228</v>
+        <v>0.00746650017863547</v>
       </c>
     </row>
     <row r="81">
@@ -4031,10 +4031,10 @@
         <v>94</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0421616199056605</v>
+        <v>0.0412834945720465</v>
       </c>
       <c r="D81" t="n">
-        <v>0.00521934614397157</v>
+        <v>0.00497579739092518</v>
       </c>
     </row>
     <row r="82">
@@ -4045,10 +4045,10 @@
         <v>48</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0367734249877948</v>
+        <v>0.0371641827105098</v>
       </c>
       <c r="D82" t="n">
-        <v>0.00215231362767521</v>
+        <v>0.00217478038726918</v>
       </c>
     </row>
     <row r="83">
@@ -4059,7 +4059,7 @@
         <v>156</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0356129622135409</v>
+        <v>0.0360355383116174</v>
       </c>
       <c r="D83"/>
     </row>
@@ -4071,7 +4071,7 @@
         <v>157</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0326766744498864</v>
+        <v>0.0330530643969582</v>
       </c>
       <c r="D84"/>
     </row>
@@ -4083,10 +4083,10 @@
         <v>95</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0324612854416281</v>
+        <v>0.0327804774019355</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0183800691174522</v>
+        <v>0.018549692324925</v>
       </c>
     </row>
     <row r="86">
@@ -4097,10 +4097,10 @@
         <v>125</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0313998206512402</v>
+        <v>0.0313504675737276</v>
       </c>
       <c r="D86" t="n">
-        <v>0.00346801925757463</v>
+        <v>0.0034740425524453</v>
       </c>
     </row>
     <row r="87">
@@ -4111,10 +4111,10 @@
         <v>102</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0308869483731085</v>
+        <v>0.0311903454428294</v>
       </c>
       <c r="D87" t="n">
-        <v>0.00415267304237246</v>
+        <v>0.00419345281281257</v>
       </c>
     </row>
     <row r="88">
@@ -4125,10 +4125,10 @@
         <v>96</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0291859890798868</v>
+        <v>0.0294692514044214</v>
       </c>
       <c r="D88" t="n">
-        <v>0.017954661784391</v>
+        <v>0.0181261956893871</v>
       </c>
     </row>
     <row r="89">
@@ -4139,10 +4139,10 @@
         <v>73</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0289131496577158</v>
+        <v>0.0292124903034522</v>
       </c>
       <c r="D89" t="n">
-        <v>0.00360430450124728</v>
+        <v>0.00364014967202993</v>
       </c>
     </row>
     <row r="90">
@@ -4153,10 +4153,10 @@
         <v>61</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0270327884912382</v>
+        <v>0.0272895431596136</v>
       </c>
       <c r="D90" t="n">
-        <v>0.00563254898061451</v>
+        <v>0.00568488609869415</v>
       </c>
     </row>
     <row r="91">
@@ -4167,10 +4167,10 @@
         <v>93</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0247045009268554</v>
+        <v>0.0249634061106773</v>
       </c>
       <c r="D91" t="n">
-        <v>0.00424447822684661</v>
+        <v>0.00429192290938485</v>
       </c>
     </row>
     <row r="92">
@@ -4181,10 +4181,10 @@
         <v>111</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0246198488651629</v>
+        <v>0.024857967494551</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0054872268437639</v>
+        <v>0.00553848088944239</v>
       </c>
     </row>
     <row r="93">
@@ -4195,10 +4195,10 @@
         <v>75</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0222404497827114</v>
+        <v>0.0224664616463471</v>
       </c>
       <c r="D93" t="n">
-        <v>0.00267571236202619</v>
+        <v>0.00270135199027758</v>
       </c>
     </row>
     <row r="94">
@@ -4209,10 +4209,10 @@
         <v>57</v>
       </c>
       <c r="C94" t="n">
-        <v>0.020339559490395</v>
+        <v>0.020570205265671</v>
       </c>
       <c r="D94" t="n">
-        <v>0.00267023546711689</v>
+        <v>0.00270189861788245</v>
       </c>
     </row>
     <row r="95">
@@ -4223,10 +4223,10 @@
         <v>40</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0201036858397776</v>
+        <v>0.0203050934801799</v>
       </c>
       <c r="D95" t="n">
-        <v>0.00699142257046306</v>
+        <v>0.00705913689371762</v>
       </c>
     </row>
     <row r="96">
@@ -4237,10 +4237,10 @@
         <v>38</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0192069211326355</v>
+        <v>0.0194053745671841</v>
       </c>
       <c r="D96" t="n">
-        <v>0.000899553026304408</v>
+        <v>0.000908807680103533</v>
       </c>
     </row>
     <row r="97">
@@ -4251,10 +4251,10 @@
         <v>158</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0186910462196303</v>
+        <v>0.0188860832095411</v>
       </c>
       <c r="D97" t="n">
-        <v>0.00560818674162251</v>
+        <v>0.00567026701110262</v>
       </c>
     </row>
     <row r="98">
@@ -4265,10 +4265,10 @@
         <v>79</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0178363406424568</v>
+        <v>0.017374339934172</v>
       </c>
       <c r="D98" t="n">
-        <v>0.00239426665865224</v>
+        <v>0.00225650153118272</v>
       </c>
     </row>
     <row r="99">
@@ -4279,10 +4279,10 @@
         <v>92</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0148201827911675</v>
+        <v>0.0149867624993856</v>
       </c>
       <c r="D99" t="n">
-        <v>0.00996743425827934</v>
+        <v>0.0100804739075933</v>
       </c>
     </row>
     <row r="100">
@@ -4293,10 +4293,10 @@
         <v>90</v>
       </c>
       <c r="C100" t="n">
-        <v>0.013509388097581</v>
+        <v>0.0136648401603512</v>
       </c>
       <c r="D100" t="n">
-        <v>0.0030382550755874</v>
+        <v>0.00307600468567943</v>
       </c>
     </row>
     <row r="101">
@@ -4307,10 +4307,10 @@
         <v>159</v>
       </c>
       <c r="C101" t="n">
-        <v>0.013303474070479</v>
+        <v>0.0135260661503676</v>
       </c>
       <c r="D101" t="n">
-        <v>0.00621949641484155</v>
+        <v>0.00634732249358989</v>
       </c>
     </row>
     <row r="102">
@@ -4321,10 +4321,10 @@
         <v>88</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0132314108335153</v>
+        <v>0.0133690643021268</v>
       </c>
       <c r="D102" t="n">
-        <v>0.0063332990493948</v>
+        <v>0.00639011660638637</v>
       </c>
     </row>
     <row r="103">
@@ -4335,10 +4335,10 @@
         <v>106</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0130581921639247</v>
+        <v>0.0132020281636138</v>
       </c>
       <c r="D103" t="n">
-        <v>0.00355034122475857</v>
+        <v>0.00359078577135605</v>
       </c>
     </row>
     <row r="104">
@@ -4349,10 +4349,10 @@
         <v>89</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0116857433676025</v>
+        <v>0.0118132779003281</v>
       </c>
       <c r="D104" t="n">
-        <v>0.00605866919801713</v>
+        <v>0.00612462167662601</v>
       </c>
     </row>
     <row r="105">
@@ -4363,10 +4363,10 @@
         <v>86</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0109911560752753</v>
+        <v>0.0111097776255183</v>
       </c>
       <c r="D105" t="n">
-        <v>0.0038344064565906</v>
+        <v>0.0038724545052133</v>
       </c>
     </row>
     <row r="106">
@@ -4377,10 +4377,10 @@
         <v>72</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0109140439633761</v>
+        <v>0.0110308277398645</v>
       </c>
       <c r="D106" t="n">
-        <v>0.00160511214397644</v>
+        <v>0.00162226739298024</v>
       </c>
     </row>
     <row r="107">
@@ -4391,10 +4391,10 @@
         <v>122</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0102790645337226</v>
+        <v>0.0103933697066224</v>
       </c>
       <c r="D107" t="n">
-        <v>0.00023156854493671</v>
+        <v>0.000223780193696136</v>
       </c>
     </row>
     <row r="108">
@@ -4405,10 +4405,10 @@
         <v>76</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0095866569318961</v>
+        <v>0.00968295542419775</v>
       </c>
       <c r="D108" t="n">
-        <v>0.00108480281586065</v>
+        <v>0.00109529121465298</v>
       </c>
     </row>
     <row r="109">
@@ -4419,10 +4419,10 @@
         <v>113</v>
       </c>
       <c r="C109" t="n">
-        <v>0.00707876731859912</v>
+        <v>0.00715195722755681</v>
       </c>
       <c r="D109" t="n">
-        <v>0.0025948448933685</v>
+        <v>0.00262226374503717</v>
       </c>
     </row>
     <row r="110">
@@ -4433,10 +4433,10 @@
         <v>49</v>
       </c>
       <c r="C110" t="n">
-        <v>0.006937888138683</v>
+        <v>0.00701747080021754</v>
       </c>
       <c r="D110" t="n">
-        <v>0.00130603710284864</v>
+        <v>0.00132051999106952</v>
       </c>
     </row>
     <row r="111">
@@ -4447,7 +4447,7 @@
         <v>127</v>
       </c>
       <c r="C111" t="n">
-        <v>0.00677538998767775</v>
+        <v>0.00684935715402428</v>
       </c>
       <c r="D111"/>
     </row>
@@ -4459,7 +4459,7 @@
         <v>91</v>
       </c>
       <c r="C112" t="n">
-        <v>0.00662187749955316</v>
+        <v>0.0066957000692075</v>
       </c>
       <c r="D112"/>
     </row>
@@ -4471,10 +4471,10 @@
         <v>81</v>
       </c>
       <c r="C113" t="n">
-        <v>0.00646620756266763</v>
+        <v>0.00653474735947246</v>
       </c>
       <c r="D113" t="n">
-        <v>0.00300571182071141</v>
+        <v>0.00303736551909417</v>
       </c>
     </row>
     <row r="114">
@@ -4485,10 +4485,10 @@
         <v>42</v>
       </c>
       <c r="C114" t="n">
-        <v>0.00642572759622504</v>
+        <v>0.00649425102915698</v>
       </c>
       <c r="D114" t="n">
-        <v>0.000926806877616954</v>
+        <v>0.00093680513191265</v>
       </c>
     </row>
     <row r="115">
@@ -4499,7 +4499,7 @@
         <v>160</v>
       </c>
       <c r="C115" t="n">
-        <v>0.00542925316954325</v>
+        <v>0.0054828978308735</v>
       </c>
       <c r="D115"/>
     </row>
@@ -4511,7 +4511,7 @@
         <v>161</v>
       </c>
       <c r="C116" t="n">
-        <v>0.00532000174362787</v>
+        <v>0.00538378957236859</v>
       </c>
       <c r="D116"/>
     </row>
@@ -4523,10 +4523,10 @@
         <v>97</v>
       </c>
       <c r="C117" t="n">
-        <v>0.00523837455854859</v>
+        <v>0.00529554618297272</v>
       </c>
       <c r="D117" t="n">
-        <v>0.00159602646511648</v>
+        <v>0.0016137263583178</v>
       </c>
     </row>
     <row r="118">
@@ -4537,10 +4537,10 @@
         <v>109</v>
       </c>
       <c r="C118" t="n">
-        <v>0.00510403445013472</v>
+        <v>0.00516083527486673</v>
       </c>
       <c r="D118" t="n">
-        <v>0.000147521933680138</v>
+        <v>0.000150430195464483</v>
       </c>
     </row>
     <row r="119">
@@ -4551,7 +4551,7 @@
         <v>119</v>
       </c>
       <c r="C119" t="n">
-        <v>0.0049331066797439</v>
+        <v>0.00499054416523633</v>
       </c>
       <c r="D119"/>
     </row>
@@ -4563,10 +4563,10 @@
         <v>50</v>
       </c>
       <c r="C120" t="n">
-        <v>0.00478671154835647</v>
+        <v>0.00483803193232979</v>
       </c>
       <c r="D120" t="n">
-        <v>0.00130298323785388</v>
+        <v>0.00131640713405925</v>
       </c>
     </row>
     <row r="121">
@@ -4577,7 +4577,7 @@
         <v>162</v>
       </c>
       <c r="C121" t="n">
-        <v>0.00424857265380789</v>
+        <v>0.004292274292291</v>
       </c>
       <c r="D121"/>
     </row>
@@ -4589,10 +4589,10 @@
         <v>163</v>
       </c>
       <c r="C122" t="n">
-        <v>0.0038259351140595</v>
+        <v>0.00386589552399151</v>
       </c>
       <c r="D122" t="n">
-        <v>0.000979104747787664</v>
+        <v>0.000988899685485546</v>
       </c>
     </row>
     <row r="123">
@@ -4603,7 +4603,7 @@
         <v>164</v>
       </c>
       <c r="C123" t="n">
-        <v>0.0037208651352272</v>
+        <v>0.00375621422137431</v>
       </c>
       <c r="D123"/>
     </row>
@@ -4615,10 +4615,10 @@
         <v>141</v>
       </c>
       <c r="C124" t="n">
-        <v>0.00346355044743912</v>
+        <v>0.00349581653198429</v>
       </c>
       <c r="D124" t="n">
-        <v>0.00225518258381621</v>
+        <v>0.00227600869864577</v>
       </c>
     </row>
     <row r="125">
@@ -4629,7 +4629,7 @@
         <v>142</v>
       </c>
       <c r="C125" t="n">
-        <v>0.00338623815988174</v>
+        <v>0.0034234439327952</v>
       </c>
       <c r="D125"/>
     </row>
@@ -4641,10 +4641,10 @@
         <v>55</v>
       </c>
       <c r="C126" t="n">
-        <v>0.00252626129037477</v>
+        <v>0.00255400747522928</v>
       </c>
       <c r="D126" t="n">
-        <v>0.00049408838683318</v>
+        <v>0.000499529202412927</v>
       </c>
     </row>
     <row r="127">
@@ -4655,7 +4655,7 @@
         <v>165</v>
       </c>
       <c r="C127" t="n">
-        <v>0.00252528265382341</v>
+        <v>0.002549652548355</v>
       </c>
       <c r="D127"/>
     </row>
@@ -4667,7 +4667,7 @@
         <v>123</v>
       </c>
       <c r="C128" t="n">
-        <v>0.00238607160439255</v>
+        <v>0.0024101377518413</v>
       </c>
       <c r="D128"/>
     </row>
@@ -4679,10 +4679,10 @@
         <v>78</v>
       </c>
       <c r="C129" t="n">
-        <v>0.00238560452785668</v>
+        <v>0.002408790867241</v>
       </c>
       <c r="D129" t="n">
-        <v>0.000439203678693502</v>
+        <v>0.000443342732240052</v>
       </c>
     </row>
     <row r="130">
@@ -4693,10 +4693,10 @@
         <v>121</v>
       </c>
       <c r="C130" t="n">
-        <v>0.00225041923333027</v>
+        <v>0.00227428199182506</v>
       </c>
       <c r="D130" t="n">
-        <v>0.00105920119290938</v>
+        <v>0.00107021790321852</v>
       </c>
     </row>
     <row r="131">
@@ -4707,10 +4707,10 @@
         <v>60</v>
       </c>
       <c r="C131" t="n">
-        <v>0.00198354059742664</v>
+        <v>0.00200447855830966</v>
       </c>
       <c r="D131" t="n">
-        <v>0.000132251780719164</v>
+        <v>0.000133255183443219</v>
       </c>
     </row>
     <row r="132">
@@ -4721,10 +4721,10 @@
         <v>166</v>
       </c>
       <c r="C132" t="n">
-        <v>0.00198338490524801</v>
+        <v>0.00200369287562616</v>
       </c>
       <c r="D132" t="n">
-        <v>0.00119184511494118</v>
+        <v>0.00120425109626506</v>
       </c>
     </row>
     <row r="133">
@@ -4735,10 +4735,10 @@
         <v>146</v>
       </c>
       <c r="C133" t="n">
-        <v>0.00158503534536518</v>
+        <v>0.001600256041685</v>
       </c>
       <c r="D133" t="n">
-        <v>0.000438099252088905</v>
+        <v>0.000442528587037495</v>
       </c>
     </row>
     <row r="134">
@@ -4749,10 +4749,10 @@
         <v>124</v>
       </c>
       <c r="C134" t="n">
-        <v>0.0015777845381892</v>
+        <v>0.00159796633786451</v>
       </c>
       <c r="D134" t="n">
-        <v>0.000554544070528963</v>
+        <v>0.000561450505832463</v>
       </c>
     </row>
     <row r="135">
@@ -4763,10 +4763,10 @@
         <v>134</v>
       </c>
       <c r="C135" t="n">
-        <v>0.0015071447725729</v>
+        <v>0.00152258569640143</v>
       </c>
       <c r="D135" t="n">
-        <v>0.000169472337695931</v>
+        <v>0.000171334740297678</v>
       </c>
     </row>
     <row r="136">
@@ -4777,10 +4777,10 @@
         <v>151</v>
       </c>
       <c r="C136" t="n">
-        <v>0.00122325120571949</v>
+        <v>0.00123459932078208</v>
       </c>
       <c r="D136" t="n">
-        <v>0.000443761074703495</v>
+        <v>0.000447877851137056</v>
       </c>
     </row>
     <row r="137">
@@ -4791,7 +4791,7 @@
         <v>129</v>
       </c>
       <c r="C137" t="n">
-        <v>0.00111844812776484</v>
+        <v>0.00112985659503261</v>
       </c>
       <c r="D137"/>
     </row>
@@ -4803,10 +4803,10 @@
         <v>136</v>
       </c>
       <c r="C138" t="n">
-        <v>0.00109311478612851</v>
+        <v>0.00110752075874442</v>
       </c>
       <c r="D138" t="n">
-        <v>0.000589757461734702</v>
+        <v>0.000597482640865109</v>
       </c>
     </row>
     <row r="139">
@@ -4817,7 +4817,7 @@
         <v>126</v>
       </c>
       <c r="C139" t="n">
-        <v>0.00102125172482302</v>
+        <v>0.00103247683843141</v>
       </c>
       <c r="D139"/>
     </row>
@@ -4829,7 +4829,7 @@
         <v>167</v>
       </c>
       <c r="C140" t="n">
-        <v>0.00093077232730189</v>
+        <v>0.000939878522161256</v>
       </c>
       <c r="D140"/>
     </row>
@@ -4841,7 +4841,7 @@
         <v>115</v>
       </c>
       <c r="C141" t="n">
-        <v>0.000752504782775876</v>
+        <v>0.000760765318398934</v>
       </c>
       <c r="D141"/>
     </row>
@@ -4853,7 +4853,7 @@
         <v>168</v>
       </c>
       <c r="C142" t="n">
-        <v>0.000744608965145591</v>
+        <v>0.000751516710810254</v>
       </c>
       <c r="D142"/>
     </row>
@@ -4865,10 +4865,10 @@
         <v>137</v>
       </c>
       <c r="C143" t="n">
-        <v>0.000737625058847254</v>
+        <v>0.000745702658952322</v>
       </c>
       <c r="D143" t="n">
-        <v>0.000120785549111243</v>
+        <v>0.00012122353094463</v>
       </c>
     </row>
     <row r="144">
@@ -4879,10 +4879,10 @@
         <v>169</v>
       </c>
       <c r="C144" t="n">
-        <v>0.000691940525290619</v>
+        <v>0.000699437172932251</v>
       </c>
       <c r="D144" t="n">
-        <v>0.000173346135716683</v>
+        <v>0.000175716182736292</v>
       </c>
     </row>
     <row r="145">
@@ -4893,7 +4893,7 @@
         <v>170</v>
       </c>
       <c r="C145" t="n">
-        <v>0.000647701704821219</v>
+        <v>0.000656381761876212</v>
       </c>
       <c r="D145"/>
     </row>
@@ -4905,7 +4905,7 @@
         <v>104</v>
       </c>
       <c r="C146" t="n">
-        <v>0.000639027426297807</v>
+        <v>0.00064594340622394</v>
       </c>
       <c r="D146"/>
     </row>
@@ -4917,10 +4917,10 @@
         <v>87</v>
       </c>
       <c r="C147" t="n">
-        <v>0.000628862951207552</v>
+        <v>0.000636335629408515</v>
       </c>
       <c r="D147" t="n">
-        <v>0.0000133052831442854</v>
+        <v>0.0000141747562044723</v>
       </c>
     </row>
     <row r="148">
@@ -4931,7 +4931,7 @@
         <v>139</v>
       </c>
       <c r="C148" t="n">
-        <v>0.000566808497155452</v>
+        <v>0.000574266697411671</v>
       </c>
       <c r="D148"/>
     </row>
@@ -4943,7 +4943,7 @@
         <v>82</v>
       </c>
       <c r="C149" t="n">
-        <v>0.000562137731796692</v>
+        <v>0.000568564885937097</v>
       </c>
       <c r="D149"/>
     </row>
@@ -4955,10 +4955,10 @@
         <v>171</v>
       </c>
       <c r="C150" t="n">
-        <v>0.000562137731796692</v>
+        <v>0.000568564885937097</v>
       </c>
       <c r="D150" t="n">
-        <v>0.000122704277886187</v>
+        <v>0.000123556889468771</v>
       </c>
     </row>
     <row r="151">
@@ -4969,7 +4969,7 @@
         <v>132</v>
       </c>
       <c r="C151" t="n">
-        <v>0.000555910044651679</v>
+        <v>0.000561291709095513</v>
       </c>
       <c r="D151"/>
     </row>
@@ -4981,7 +4981,7 @@
         <v>131</v>
       </c>
       <c r="C152" t="n">
-        <v>0.000490452604409625</v>
+        <v>0.000495541292524534</v>
       </c>
       <c r="D152"/>
     </row>
@@ -4993,7 +4993,7 @@
         <v>172</v>
       </c>
       <c r="C153" t="n">
-        <v>0.000439519020259335</v>
+        <v>0.000444696398863467</v>
       </c>
       <c r="D153"/>
     </row>
@@ -5005,7 +5005,7 @@
         <v>98</v>
       </c>
       <c r="C154" t="n">
-        <v>0.000362051040523327</v>
+        <v>0.000365409792059541</v>
       </c>
       <c r="D154"/>
     </row>
@@ -5017,10 +5017,10 @@
         <v>173</v>
       </c>
       <c r="C155" t="n">
-        <v>0.000360738777874913</v>
+        <v>0.000365275103599512</v>
       </c>
       <c r="D155" t="n">
-        <v>0.000111301996231806</v>
+        <v>0.000113017093142041</v>
       </c>
     </row>
     <row r="156">
@@ -5031,7 +5031,7 @@
         <v>174</v>
       </c>
       <c r="C156" t="n">
-        <v>0.000342811935593195</v>
+        <v>0.00034630647881205</v>
       </c>
       <c r="D156"/>
     </row>
@@ -5043,7 +5043,7 @@
         <v>175</v>
       </c>
       <c r="C157" t="n">
-        <v>0.000215010898681595</v>
+        <v>0.000217364726410649</v>
       </c>
       <c r="D157"/>
     </row>
@@ -5055,7 +5055,7 @@
         <v>176</v>
       </c>
       <c r="C158" t="n">
-        <v>0.000205691609703878</v>
+        <v>0.000207779397671895</v>
       </c>
       <c r="D158"/>
     </row>
@@ -5067,7 +5067,7 @@
         <v>177</v>
       </c>
       <c r="C159" t="n">
-        <v>0.000194303838924424</v>
+        <v>0.000196914528562864</v>
       </c>
       <c r="D159"/>
     </row>
@@ -5079,7 +5079,7 @@
         <v>138</v>
       </c>
       <c r="C160" t="n">
-        <v>0.000129535892616283</v>
+        <v>0.000131276352375242</v>
       </c>
       <c r="D160"/>
     </row>
@@ -5091,7 +5091,7 @@
         <v>114</v>
       </c>
       <c r="C161" t="n">
-        <v>0.000101666992642347</v>
+        <v>0.000102722398849027</v>
       </c>
       <c r="D161"/>
     </row>
@@ -5103,7 +5103,7 @@
         <v>178</v>
       </c>
       <c r="C162" t="n">
-        <v>0.000101666992642347</v>
+        <v>0.000102722398849027</v>
       </c>
       <c r="D162"/>
     </row>
